--- a/InFiRA-QA/688578-QA.xlsx
+++ b/InFiRA-QA/688578-QA.xlsx
@@ -1067,7 +1067,7 @@
         <v>49</v>
       </c>
       <c r="B35" s="5">
-        <v>393.89</v>
+        <v>393.87</v>
       </c>
       <c r="C35" t="s">
         <v>4</v>
